--- a/output/pdf_financials_xlsx/GGD.xlsx
+++ b/output/pdf_financials_xlsx/GGD.xlsx
@@ -1363,13 +1363,13 @@
         <v>-0.772799</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2.404699</v>
+        <v>-2.404699</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>3.642722</v>
+        <v>-3.642722</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>7.206897</v>
+        <v>-7.206897</v>
       </c>
       <c r="G16" s="1" t="inlineStr">
         <is>
@@ -1663,13 +1663,13 @@
         <v>-0.772799</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2.404699</v>
+        <v>-2.404699</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>3.642722</v>
+        <v>-3.642722</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>7.206897</v>
+        <v>-7.206897</v>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
@@ -1854,13 +1854,13 @@
         <v>-0.772799</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.404699</v>
+        <v>-2.404699</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>3.642722</v>
+        <v>-3.642722</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>7.206897</v>
+        <v>-7.206897</v>
       </c>
       <c r="G23" s="1" t="inlineStr">
         <is>
@@ -2180,13 +2180,13 @@
         <v>-0.772799</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>2.404699</v>
+        <v>-2.404699</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>3.40985</v>
+        <v>-3.875594</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>7.206897</v>
+        <v>-7.206897</v>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
@@ -2304,13 +2304,13 @@
         <v>-0.7681519999999999</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2.412974</v>
+        <v>-2.396424</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>3.441198</v>
+        <v>-3.844246</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>7.260523</v>
+        <v>-7.153271</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -2456,13 +2456,13 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="1" t="inlineStr">
         <is>
@@ -7350,13 +7350,13 @@
         <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-10.212451</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-4.951462</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-4.555</v>
       </c>
       <c r="H118" s="1" t="inlineStr">
         <is>
@@ -7364,10 +7364,10 @@
         </is>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-2.342</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-3.194</v>
       </c>
       <c r="K118" s="3" t="n">
         <v>0</v>
@@ -7378,19 +7378,19 @@
         </is>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-8.679</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-19.424</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-24.492</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-13.863</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-9.992000000000001</v>
       </c>
     </row>
     <row r="119">
@@ -18226,7 +18226,11 @@
           <t>Exploration and evaluation expenditures (Note 7) (13,309)</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -20764,7 +20768,11 @@
           <t>Exploration and evaluation expenditures (Note 8) (9,992)</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -23488,7 +23496,11 @@
           <t>Exploration and evaluation expenditures (Note 8) (13,863)</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -25838,7 +25850,11 @@
           <t>Exploration and evaluation expenditures (Note 7) (24,492)</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -28384,7 +28400,11 @@
           <t>Exploration and evaluation expenditures (Note 7) (19,424)</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
@@ -31408,7 +31428,11 @@
           <t>Exploration and evaluation expenditures (Note 8) (2,695)</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -34244,7 +34268,11 @@
           <t>Exploration and evaluation expenditures -</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
@@ -36988,7 +37016,11 @@
           <t>Exploration and evaluation expenditures (3,194)</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -39718,7 +39750,11 @@
           <t>Exploration and evaluation expenditures (6,831)</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>-</t>
@@ -42038,7 +42074,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr"/>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E352" t="inlineStr">
         <is>
           <t>-</t>
@@ -65377,10 +65417,10 @@
         </is>
       </c>
       <c r="H593" s="5" t="n">
-        <v>3.642722</v>
+        <v>-3.642722</v>
       </c>
       <c r="I593" s="5" t="n">
-        <v>7.206897</v>
+        <v>-7.206897</v>
       </c>
       <c r="J593" t="inlineStr">
         <is>
@@ -65562,13 +65602,13 @@
         </is>
       </c>
       <c r="G595" s="5" t="n">
-        <v>2.34062</v>
+        <v>-2.34062</v>
       </c>
       <c r="H595" s="5" t="n">
-        <v>3.695619</v>
+        <v>-3.695619</v>
       </c>
       <c r="I595" s="5" t="n">
-        <v>5.709224</v>
+        <v>-5.709224</v>
       </c>
       <c r="J595" t="inlineStr">
         <is>
@@ -66138,10 +66178,10 @@
         </is>
       </c>
       <c r="G601" s="5" t="n">
-        <v>2.404699</v>
+        <v>-2.404699</v>
       </c>
       <c r="H601" s="5" t="n">
-        <v>3.642722</v>
+        <v>-3.642722</v>
       </c>
       <c r="I601" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/GGD.xlsx
+++ b/output/pdf_financials_xlsx/GGD.xlsx
@@ -1148,21 +1148,19 @@
         </is>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.076</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.31</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>5.688</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>4.428</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>4.824</v>
       </c>
     </row>
     <row r="13">
@@ -2215,10 +2213,10 @@
         </is>
       </c>
       <c r="M27" s="3" t="n">
-        <v>43.148</v>
+        <v>43.072</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>8.381</v>
+        <v>8.071</v>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
@@ -2226,10 +2224,10 @@
         </is>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-10.004</v>
+        <v>-14.432</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>7.306</v>
+        <v>2.482</v>
       </c>
     </row>
     <row r="28">
@@ -2339,10 +2337,10 @@
         </is>
       </c>
       <c r="M29" s="3" t="n">
-        <v>46.842</v>
+        <v>46.766</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>13.404</v>
+        <v>13.094</v>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
@@ -2350,10 +2348,10 @@
         </is>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-6.872</v>
+        <v>-11.3</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>10.108</v>
+        <v>5.284</v>
       </c>
     </row>
     <row r="30">
@@ -2609,25 +2607,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.66832</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.596623</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>24.727903</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>30.199</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>3.412</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>2.721</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>2.091</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>4.606</v>
@@ -2719,25 +2717,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.27555</v>
+        <v>0.94387</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.277617</v>
+        <v>1.87424</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>24.727903</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>30.199</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>3.412</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>2.721</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>2.091</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>4.606</v>
@@ -3379,25 +3377,25 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.7151420000000001</v>
+        <v>0.046822</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.117466</v>
+        <v>0.5208429999999999</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>25.351962</v>
+        <v>0.624059</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>30.624</v>
+        <v>0.425</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>9.869999999999999</v>
+        <v>6.458</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>4.561</v>
+        <v>1.84</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>5.055</v>
+        <v>2.964</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>28.873</v>
@@ -13514,7 +13512,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -15148,7 +15146,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
@@ -47154,7 +47152,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -49006,7 +49004,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -50954,7 +50952,7 @@
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
@@ -52894,7 +52892,7 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
@@ -54754,7 +54752,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">

--- a/output/pdf_financials_xlsx/GGD.xlsx
+++ b/output/pdf_financials_xlsx/GGD.xlsx
@@ -7480,7 +7480,7 @@
         </is>
       </c>
       <c r="I120" s="3" t="n">
-        <v>0</v>
+        <v>7.454</v>
       </c>
       <c r="J120" s="3" t="n">
         <v>0</v>
@@ -37604,7 +37604,11 @@
           <t>Issuance of common shares (net of issuance costs) (Note 12) -</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -40334,7 +40338,11 @@
           <t>Issuance of common shares (net of issuance costs) (Note 11) 16,194</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E334" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GGD.xlsx
+++ b/output/pdf_financials_xlsx/GGD.xlsx
@@ -1355,10 +1355,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.321499</v>
+        <v>-0.642998</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-0.772799</v>
+        <v>-0.597799</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-2.404699</v>
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>-20.537</v>
+        <v>-20.574</v>
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>-43.693</v>
+        <v>-43.678</v>
       </c>
       <c r="L16" s="1" t="inlineStr">
         <is>
@@ -1420,10 +1420,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>0.321499</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.175</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -1443,15 +1443,13 @@
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
-      </c>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.037</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>-0.062</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.015</v>
       </c>
       <c r="L17" s="1" t="inlineStr">
         <is>
@@ -1680,12 +1678,10 @@
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-20.437</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>-73.245</v>
@@ -1743,15 +1739,13 @@
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.1</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>0.8179999999999999</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
+        <v>29.552</v>
       </c>
       <c r="L21" s="1" t="inlineStr">
         <is>
@@ -2172,10 +2166,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.321499</v>
+        <v>-0.642998</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.772799</v>
+        <v>-0.597799</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-2.404699</v>
@@ -2197,7 +2191,7 @@
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-20.537</v>
+        <v>-20.574</v>
       </c>
       <c r="J27" s="1" t="inlineStr">
         <is>
@@ -2205,7 +2199,7 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-43.801</v>
+        <v>-43.786</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -2296,10 +2290,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.321499</v>
+        <v>-0.642998</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.7681519999999999</v>
+        <v>-0.593152</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-2.396424</v>
@@ -2321,7 +2315,7 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-16.779</v>
+        <v>-16.816</v>
       </c>
       <c r="J29" s="1" t="inlineStr">
         <is>
@@ -2329,7 +2323,7 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-38.679</v>
+        <v>-38.664</v>
       </c>
       <c r="L29" s="1" t="inlineStr">
         <is>
@@ -2448,10 +2442,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0</v>
+        <v>-50</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-29.27405365348554</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -2473,7 +2467,7 @@
         </is>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.1798386312822008</v>
       </c>
       <c r="J31" s="1" t="inlineStr">
         <is>
@@ -2481,7 +2475,7 @@
         </is>
       </c>
       <c r="K31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.03434223178716974</v>
       </c>
       <c r="L31" s="1" t="inlineStr">
         <is>
@@ -6668,19 +6662,19 @@
         </is>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0</v>
+        <v>-2.801</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0</v>
+        <v>-6.485</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0</v>
+        <v>-10.767</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>0</v>
+        <v>-13.208</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>0</v>
+        <v>-19.028</v>
       </c>
     </row>
     <row r="107">
@@ -6758,7 +6752,7 @@
         <v>0</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>0</v>
+        <v>0.715098</v>
       </c>
       <c r="F108" s="3" t="n">
         <v>0</v>
@@ -6772,13 +6766,13 @@
         </is>
       </c>
       <c r="I108" s="3" t="n">
-        <v>0</v>
+        <v>20.03</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>0</v>
+        <v>0.345</v>
       </c>
       <c r="K108" s="3" t="n">
-        <v>0</v>
+        <v>48.157</v>
       </c>
       <c r="L108" s="1" t="inlineStr">
         <is>
@@ -7199,7 +7193,7 @@
         </is>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>5.041</v>
       </c>
       <c r="N115" s="3" t="n">
         <v>0</v>
@@ -16784,7 +16778,11 @@
           <t>Deferred income tax expense 2,224</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -18028,7 +18026,11 @@
           <t>Net change in non-cash operating working capital (Note 13) (988)</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -19406,7 +19408,11 @@
           <t>Net income (loss) $ 1,580 $</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -20570,7 +20576,11 @@
           <t>Net change in non-cash operating working capital (Note 14) (19,028)</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -22812,7 +22822,11 @@
           <t>Impairment charge (Note 7) 2,980</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -23298,7 +23312,11 @@
           <t>Net change in non-cash operating working capital (Note 14) (13,208)</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -25652,7 +25670,11 @@
           <t>Net change in non-cash operating working capital (Note 13) (10,767)</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -28202,7 +28224,11 @@
           <t>Net change in non-cash operating working capital (Note 14) (6,485)</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -28498,7 +28524,11 @@
           <t>Net proceeds on sale of marketable securities -</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -30652,7 +30682,11 @@
           <t>Impairment charge (Note 12) -</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -31528,7 +31562,11 @@
           <t>Net proceeds on sale of marketable securities (Note 5) 4,582</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -33582,7 +33620,11 @@
           <t>Impairment charge (Note 5) 48,157</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E265" t="inlineStr">
         <is>
           <t>-</t>
@@ -36626,7 +36668,11 @@
           <t>Impairment charge 345</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -41312,7 +41358,11 @@
           <t>Impairment charge</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr"/>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
           <t>-</t>
@@ -44206,7 +44256,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr"/>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E374" t="inlineStr">
         <is>
           <t>-</t>
@@ -57192,7 +57246,11 @@
           <t>Current income tax recovery (Note 11) -</t>
         </is>
       </c>
-      <c r="D508" t="inlineStr"/>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E508" t="inlineStr">
         <is>
           <t>-</t>
@@ -57484,7 +57542,11 @@
           <t>Net income from discontinued operations (Note 13) -</t>
         </is>
       </c>
-      <c r="D511" t="inlineStr"/>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E511" t="inlineStr">
         <is>
           <t>-</t>
@@ -59040,7 +59102,11 @@
           <t>Interest revenue 108</t>
         </is>
       </c>
-      <c r="D527" t="inlineStr"/>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E527" t="inlineStr">
         <is>
           <t>-</t>
@@ -59330,7 +59396,11 @@
           <t>Current income tax recovery (Note 13) 15</t>
         </is>
       </c>
-      <c r="D530" t="inlineStr"/>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E530" t="inlineStr">
         <is>
           <t>-</t>
@@ -59426,7 +59496,11 @@
           <t>Deferred income tax recovery (Note 13) 4,232</t>
         </is>
       </c>
-      <c r="D531" t="inlineStr"/>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E531" t="inlineStr">
         <is>
           <t>-</t>
@@ -59522,7 +59596,11 @@
           <t>Net loss from continuing operations (73,245)</t>
         </is>
       </c>
-      <c r="D532" t="inlineStr"/>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E532" t="inlineStr">
         <is>
           <t>-</t>
@@ -59618,7 +59696,11 @@
           <t>Net income from discontinued operations (Note 5) 29,552</t>
         </is>
       </c>
-      <c r="D533" t="inlineStr"/>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E533" t="inlineStr">
         <is>
           <t>-</t>
@@ -60100,7 +60182,11 @@
           <t>Net loss from continuing operations $ (0.43) $</t>
         </is>
       </c>
-      <c r="D538" t="inlineStr"/>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E538" t="inlineStr">
         <is>
           <t>-</t>
@@ -60196,7 +60282,11 @@
           <t>Net income from discontinued operations $ 0.17 $</t>
         </is>
       </c>
-      <c r="D539" t="inlineStr"/>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E539" t="inlineStr">
         <is>
           <t>-</t>
@@ -61356,7 +61446,11 @@
           <t>Current income tax recovery (expense) (Note 13) 62</t>
         </is>
       </c>
-      <c r="D551" t="inlineStr"/>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E551" t="inlineStr">
         <is>
           <t>-</t>
@@ -61452,7 +61546,11 @@
           <t>Deferred income tax recovery (Note 13) 7,597</t>
         </is>
       </c>
-      <c r="D552" t="inlineStr"/>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E552" t="inlineStr">
         <is>
           <t>-</t>
@@ -61548,7 +61646,11 @@
           <t>Net loss from continuing operations (1,402)</t>
         </is>
       </c>
-      <c r="D553" t="inlineStr"/>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E553" t="inlineStr">
         <is>
           <t>-</t>
@@ -61646,7 +61748,7 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>NetIncomeContinuousOperations</t>
+          <t>NetIncomeDiscontinuousOperations</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
@@ -66750,7 +66852,11 @@
           <t>Net loss for the year, before income tax recovery</t>
         </is>
       </c>
-      <c r="D607" t="inlineStr"/>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E607" s="5" t="n">
         <v>-0.321499</v>
       </c>
@@ -66844,7 +66950,11 @@
           <t>Income tax recovery (Note 12)</t>
         </is>
       </c>
-      <c r="D608" t="inlineStr"/>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E608" t="inlineStr">
         <is>
           <t>-</t>
